--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/44.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/44.xlsx
@@ -426,13 +426,13 @@
         <v>-9.996415003602724</v>
       </c>
       <c r="E2">
-        <v>-15.8460881375618</v>
+        <v>-17.80727966080368</v>
       </c>
       <c r="F2">
-        <v>5.810713053371864</v>
+        <v>2.650693533338033</v>
       </c>
       <c r="G2">
-        <v>-17.76450452586735</v>
+        <v>-17.71849359655004</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-9.474687439419563</v>
       </c>
       <c r="E3">
-        <v>-15.45663937290215</v>
+        <v>-17.64545917061359</v>
       </c>
       <c r="F3">
-        <v>5.846081028001792</v>
+        <v>3.52560027356162</v>
       </c>
       <c r="G3">
-        <v>-17.72402409548848</v>
+        <v>-16.54516814155132</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-8.821164351870975</v>
       </c>
       <c r="E4">
-        <v>-16.22563765804069</v>
+        <v>-18.53562583477536</v>
       </c>
       <c r="F4">
-        <v>5.640473611687732</v>
+        <v>2.774512922504087</v>
       </c>
       <c r="G4">
-        <v>-17.49698981334738</v>
+        <v>-16.88483691616348</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-8.080362208370653</v>
       </c>
       <c r="E5">
-        <v>-15.3854698753976</v>
+        <v>-21.51206047427086</v>
       </c>
       <c r="F5">
-        <v>5.433224371181324</v>
+        <v>4.332794605545571</v>
       </c>
       <c r="G5">
-        <v>-15.85823784563845</v>
+        <v>-16.12927166828092</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-7.270851195729672</v>
       </c>
       <c r="E6">
-        <v>-15.57322946470363</v>
+        <v>-20.3287747445406</v>
       </c>
       <c r="F6">
-        <v>5.733184491409053</v>
+        <v>3.572336762427569</v>
       </c>
       <c r="G6">
-        <v>-15.64293393057237</v>
+        <v>-15.97359247078229</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-6.423041870041797</v>
       </c>
       <c r="E7">
-        <v>-16.98397591536516</v>
+        <v>-20.9029807202392</v>
       </c>
       <c r="F7">
-        <v>5.794506873503495</v>
+        <v>3.500966283737169</v>
       </c>
       <c r="G7">
-        <v>-16.02788520331564</v>
+        <v>-16.39289157080983</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-5.560387098844386</v>
       </c>
       <c r="E8">
-        <v>-16.7897632505982</v>
+        <v>-20.30577462505564</v>
       </c>
       <c r="F8">
-        <v>4.906639496895706</v>
+        <v>3.363043111171051</v>
       </c>
       <c r="G8">
-        <v>-14.74541811619589</v>
+        <v>-14.66796160006364</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-4.710777558418869</v>
       </c>
       <c r="E9">
-        <v>-16.25149524462448</v>
+        <v>-19.00774189244503</v>
       </c>
       <c r="F9">
-        <v>5.953732342200004</v>
+        <v>4.027923923354046</v>
       </c>
       <c r="G9">
-        <v>-13.84983330070716</v>
+        <v>-14.0963629607437</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-3.897543885058762</v>
       </c>
       <c r="E10">
-        <v>-18.41949764732266</v>
+        <v>-23.81280603555588</v>
       </c>
       <c r="F10">
-        <v>5.828440115791773</v>
+        <v>3.939156072470051</v>
       </c>
       <c r="G10">
-        <v>-13.33352488527463</v>
+        <v>-13.17459891904293</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-3.144587748899352</v>
       </c>
       <c r="E11">
-        <v>-19.46948321616313</v>
+        <v>-23.36063790588999</v>
       </c>
       <c r="F11">
-        <v>5.725802081115304</v>
+        <v>3.3990091670658</v>
       </c>
       <c r="G11">
-        <v>-13.57426154864797</v>
+        <v>-14.82111917879384</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-2.471670070597599</v>
       </c>
       <c r="E12">
-        <v>-21.70484214125139</v>
+        <v>-23.95497747702669</v>
       </c>
       <c r="F12">
-        <v>5.541609618898416</v>
+        <v>3.372794652236807</v>
       </c>
       <c r="G12">
-        <v>-11.51044537463155</v>
+        <v>-12.96816086463046</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-1.893136151508128</v>
       </c>
       <c r="E13">
-        <v>-21.97046884111932</v>
+        <v>-24.49520631224573</v>
       </c>
       <c r="F13">
-        <v>6.023073320753545</v>
+        <v>3.872810470445033</v>
       </c>
       <c r="G13">
-        <v>-11.35212643438834</v>
+        <v>-11.28703027987052</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-1.425811056421583</v>
       </c>
       <c r="E14">
-        <v>-20.19609498458987</v>
+        <v>-23.98779079968627</v>
       </c>
       <c r="F14">
-        <v>5.725730841518662</v>
+        <v>3.833784425364343</v>
       </c>
       <c r="G14">
-        <v>-10.90618545590889</v>
+        <v>-10.56481700852894</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-1.077159185874607</v>
       </c>
       <c r="E15">
-        <v>-22.69217627219575</v>
+        <v>-25.19652202486563</v>
       </c>
       <c r="F15">
-        <v>6.004285948058052</v>
+        <v>3.691598474143419</v>
       </c>
       <c r="G15">
-        <v>-10.86528831039197</v>
+        <v>-10.52100613826724</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-0.8491839000613393</v>
       </c>
       <c r="E16">
-        <v>-23.93634280648513</v>
+        <v>-28.09864893436927</v>
       </c>
       <c r="F16">
-        <v>6.441074139145398</v>
+        <v>3.918879295184325</v>
       </c>
       <c r="G16">
-        <v>-9.886805072814642</v>
+        <v>-8.958015935755101</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-0.7385492956908597</v>
       </c>
       <c r="E17">
-        <v>-24.01511108337454</v>
+        <v>-29.37529368424165</v>
       </c>
       <c r="F17">
-        <v>6.09849617277844</v>
+        <v>4.474927541252716</v>
       </c>
       <c r="G17">
-        <v>-9.340957460293216</v>
+        <v>-10.32497283741977</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-0.7365398875719197</v>
       </c>
       <c r="E18">
-        <v>-23.51440224082044</v>
+        <v>-28.3272100744844</v>
       </c>
       <c r="F18">
-        <v>6.845671972959955</v>
+        <v>3.190876886908007</v>
       </c>
       <c r="G18">
-        <v>-8.509892944938619</v>
+        <v>-8.285673950895523</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-0.8322571194965624</v>
       </c>
       <c r="E19">
-        <v>-24.46201259776951</v>
+        <v>-28.7320375368741</v>
       </c>
       <c r="F19">
-        <v>6.307277892980028</v>
+        <v>3.443248956579711</v>
       </c>
       <c r="G19">
-        <v>-8.072200957459609</v>
+        <v>-7.900511039361665</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-1.012666180195131</v>
       </c>
       <c r="E20">
-        <v>-26.96017245494491</v>
+        <v>-28.4404445670462</v>
       </c>
       <c r="F20">
-        <v>6.347407323441247</v>
+        <v>4.257978118459525</v>
       </c>
       <c r="G20">
-        <v>-8.551866331127036</v>
+        <v>-7.607960606343133</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-1.262565791391632</v>
       </c>
       <c r="E21">
-        <v>-26.63804851335729</v>
+        <v>-30.65665257555603</v>
       </c>
       <c r="F21">
-        <v>6.07725351910105</v>
+        <v>3.484256456487897</v>
       </c>
       <c r="G21">
-        <v>-6.569257109485314</v>
+        <v>-7.050251377884315</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-1.567711395723248</v>
       </c>
       <c r="E22">
-        <v>-28.62779206521753</v>
+        <v>-30.47461018468468</v>
       </c>
       <c r="F22">
-        <v>6.406421873951489</v>
+        <v>3.744136848298575</v>
       </c>
       <c r="G22">
-        <v>-5.833886139690362</v>
+        <v>-7.180450249363082</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-1.913812218668768</v>
       </c>
       <c r="E23">
-        <v>-27.95090746986902</v>
+        <v>-32.47884258913246</v>
       </c>
       <c r="F23">
-        <v>5.845789442676006</v>
+        <v>4.524074579260811</v>
       </c>
       <c r="G23">
-        <v>-5.067986684506335</v>
+        <v>-7.343120089394112</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-2.286547591818218</v>
       </c>
       <c r="E24">
-        <v>-28.32009584181835</v>
+        <v>-31.8245958353483</v>
       </c>
       <c r="F24">
-        <v>6.022157146406049</v>
+        <v>4.012196539844495</v>
       </c>
       <c r="G24">
-        <v>-4.508197161578829</v>
+        <v>-6.358924245081789</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-2.672608717939328</v>
       </c>
       <c r="E25">
-        <v>-28.87702568917769</v>
+        <v>-33.18264896245658</v>
       </c>
       <c r="F25">
-        <v>5.830593871039052</v>
+        <v>3.450152570514641</v>
       </c>
       <c r="G25">
-        <v>-4.647481735555698</v>
+        <v>-5.234584146744022</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-3.059464625845514</v>
       </c>
       <c r="E26">
-        <v>-29.09530719329541</v>
+        <v>-32.96795400975292</v>
       </c>
       <c r="F26">
-        <v>6.283773796292994</v>
+        <v>4.037007800293146</v>
       </c>
       <c r="G26">
-        <v>-4.556017684586177</v>
+        <v>-5.544462710817981</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-3.435851723509991</v>
       </c>
       <c r="E27">
-        <v>-29.8089607333492</v>
+        <v>-31.93011380820102</v>
       </c>
       <c r="F27">
-        <v>5.785094963072886</v>
+        <v>4.245312380870721</v>
       </c>
       <c r="G27">
-        <v>-2.348589005355982</v>
+        <v>-4.713995377787202</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-3.794498409953064</v>
       </c>
       <c r="E28">
-        <v>-29.90635009535816</v>
+        <v>-30.33212627850734</v>
       </c>
       <c r="F28">
-        <v>6.310013162144071</v>
+        <v>4.746849081630486</v>
       </c>
       <c r="G28">
-        <v>-2.274515428651517</v>
+        <v>-3.610382756040447</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-4.128617294671521</v>
       </c>
       <c r="E29">
-        <v>-29.54451370096028</v>
+        <v>-31.98512797468321</v>
       </c>
       <c r="F29">
-        <v>5.843160204539521</v>
+        <v>3.72454098901795</v>
       </c>
       <c r="G29">
-        <v>-3.214313064042995</v>
+        <v>-3.45643112169286</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-4.433138218520515</v>
       </c>
       <c r="E30">
-        <v>-27.97363588091352</v>
+        <v>-32.4025876153173</v>
       </c>
       <c r="F30">
-        <v>5.69990400263418</v>
+        <v>3.962310598113103</v>
       </c>
       <c r="G30">
-        <v>-2.345022317520865</v>
+        <v>-3.554680738847314</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-4.70470719758798</v>
       </c>
       <c r="E31">
-        <v>-29.2009202641023</v>
+        <v>-30.48249652216904</v>
       </c>
       <c r="F31">
-        <v>5.776393791873881</v>
+        <v>3.588075743080759</v>
       </c>
       <c r="G31">
-        <v>-2.804475366382112</v>
+        <v>-5.097094400960169</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-4.940911011632438</v>
       </c>
       <c r="E32">
-        <v>-27.74747936049645</v>
+        <v>-31.47451988794834</v>
       </c>
       <c r="F32">
-        <v>5.568183645180224</v>
+        <v>3.432026235006583</v>
       </c>
       <c r="G32">
-        <v>-3.680906051017593</v>
+        <v>-2.128054823124143</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-5.139941775869638</v>
       </c>
       <c r="E33">
-        <v>-29.30001686081215</v>
+        <v>-31.46746452544438</v>
       </c>
       <c r="F33">
-        <v>5.960185324267813</v>
+        <v>2.78969358352779</v>
       </c>
       <c r="G33">
-        <v>-4.134055873263145</v>
+        <v>-2.459238358783577</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-5.300437332852462</v>
       </c>
       <c r="E34">
-        <v>-27.64905297793974</v>
+        <v>-30.46454112272863</v>
       </c>
       <c r="F34">
-        <v>6.074526533611033</v>
+        <v>3.966084640000258</v>
       </c>
       <c r="G34">
-        <v>-3.10478260716717</v>
+        <v>-2.70030642553442</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-5.419838775004791</v>
       </c>
       <c r="E35">
-        <v>-27.42370252589604</v>
+        <v>-29.35699412077666</v>
       </c>
       <c r="F35">
-        <v>5.728075121268585</v>
+        <v>3.360398962421315</v>
       </c>
       <c r="G35">
-        <v>-2.533265998386209</v>
+        <v>-3.013899332413671</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-5.49890425020465</v>
       </c>
       <c r="E36">
-        <v>-27.10896452541493</v>
+        <v>-30.04657202876867</v>
       </c>
       <c r="F36">
-        <v>6.035346412193423</v>
+        <v>3.777193677874692</v>
       </c>
       <c r="G36">
-        <v>-3.568258433660296</v>
+        <v>-3.687691617202524</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-5.537982716276527</v>
       </c>
       <c r="E37">
-        <v>-26.83004222586049</v>
+        <v>-28.2444386265722</v>
       </c>
       <c r="F37">
-        <v>5.716148287403078</v>
+        <v>3.711653248965195</v>
       </c>
       <c r="G37">
-        <v>-4.872826188593683</v>
+        <v>-4.688969500953317</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-5.53702306416033</v>
       </c>
       <c r="E38">
-        <v>-25.36773909862163</v>
+        <v>-28.93244515408355</v>
       </c>
       <c r="F38">
-        <v>6.467788987885682</v>
+        <v>4.176920711360788</v>
       </c>
       <c r="G38">
-        <v>-4.496128828683192</v>
+        <v>-5.379906168390269</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-5.498566230914117</v>
       </c>
       <c r="E39">
-        <v>-28.03866023918966</v>
+        <v>-29.06298747430267</v>
       </c>
       <c r="F39">
-        <v>6.850380413277468</v>
+        <v>4.327040765565726</v>
       </c>
       <c r="G39">
-        <v>-4.430793144991529</v>
+        <v>-6.426054756966469</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-5.425663970200413</v>
       </c>
       <c r="E40">
-        <v>-25.34665452364192</v>
+        <v>-27.09143933100525</v>
       </c>
       <c r="F40">
-        <v>6.574457858344174</v>
+        <v>4.706671605859905</v>
       </c>
       <c r="G40">
-        <v>-5.64764072275472</v>
+        <v>-7.059809576286978</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-5.321971363746514</v>
       </c>
       <c r="E41">
-        <v>-26.37492605961561</v>
+        <v>-26.94717120606888</v>
       </c>
       <c r="F41">
-        <v>6.56436337317366</v>
+        <v>4.359473006120131</v>
       </c>
       <c r="G41">
-        <v>-5.937608834405968</v>
+        <v>-4.972995320360411</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-5.191948985750353</v>
       </c>
       <c r="E42">
-        <v>-24.36791996483813</v>
+        <v>-25.43097470966474</v>
       </c>
       <c r="F42">
-        <v>6.700235508050445</v>
+        <v>4.377231546501347</v>
       </c>
       <c r="G42">
-        <v>-5.007533458495126</v>
+        <v>-6.147593889324193</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-5.039716418795421</v>
       </c>
       <c r="E43">
-        <v>-24.50744677748846</v>
+        <v>-21.71129521671233</v>
       </c>
       <c r="F43">
-        <v>6.638593376138523</v>
+        <v>5.251692625062229</v>
       </c>
       <c r="G43">
-        <v>-5.223460805657504</v>
+        <v>-6.222195742699728</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-4.869703428865591</v>
       </c>
       <c r="E44">
-        <v>-24.23049436412736</v>
+        <v>-23.43764913486443</v>
       </c>
       <c r="F44">
-        <v>6.765930013296863</v>
+        <v>4.116126827669332</v>
       </c>
       <c r="G44">
-        <v>-5.90457021452392</v>
+        <v>-5.05431055304657</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-4.686544911503108</v>
       </c>
       <c r="E45">
-        <v>-22.81539604994446</v>
+        <v>-24.42962042319264</v>
       </c>
       <c r="F45">
-        <v>7.248666087482692</v>
+        <v>5.058798991646336</v>
       </c>
       <c r="G45">
-        <v>-6.16462999166083</v>
+        <v>-7.090482435424667</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-4.493373267861419</v>
       </c>
       <c r="E46">
-        <v>-20.89636461971399</v>
+        <v>-21.68744374411392</v>
       </c>
       <c r="F46">
-        <v>7.959854294216985</v>
+        <v>4.158955079128872</v>
       </c>
       <c r="G46">
-        <v>-6.884890936174539</v>
+        <v>-6.638700882569402</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-4.292931206999003</v>
       </c>
       <c r="E47">
-        <v>-21.79542520682682</v>
+        <v>-22.92540626901279</v>
       </c>
       <c r="F47">
-        <v>7.73349958793241</v>
+        <v>5.003795396100449</v>
       </c>
       <c r="G47">
-        <v>-7.574780893934029</v>
+        <v>-6.73095570793475</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-4.089231045196287</v>
       </c>
       <c r="E48">
-        <v>-20.81835712645786</v>
+        <v>-23.83898967226823</v>
       </c>
       <c r="F48">
-        <v>7.460794411991589</v>
+        <v>5.045135899704561</v>
       </c>
       <c r="G48">
-        <v>-7.386484713523734</v>
+        <v>-9.014495602457824</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-3.884353664013251</v>
       </c>
       <c r="E49">
-        <v>-19.92230797456013</v>
+        <v>-22.21651441937807</v>
       </c>
       <c r="F49">
-        <v>7.695585211906276</v>
+        <v>6.060755753906895</v>
       </c>
       <c r="G49">
-        <v>-8.840206956884799</v>
+        <v>-8.661701941607888</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-3.680256680940817</v>
       </c>
       <c r="E50">
-        <v>-19.78387705261965</v>
+        <v>-18.96944458776216</v>
       </c>
       <c r="F50">
-        <v>7.995212328438079</v>
+        <v>5.831978901336533</v>
       </c>
       <c r="G50">
-        <v>-7.619172540411756</v>
+        <v>-7.878487480254672</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-3.478655698593683</v>
       </c>
       <c r="E51">
-        <v>-19.5181733686936</v>
+        <v>-17.49380963304472</v>
       </c>
       <c r="F51">
-        <v>7.570397359790798</v>
+        <v>5.939946651882615</v>
       </c>
       <c r="G51">
-        <v>-5.695103592612088</v>
+        <v>-7.791180737000967</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-3.280596737178152</v>
       </c>
       <c r="E52">
-        <v>-17.74866309324839</v>
+        <v>-20.36442742040299</v>
       </c>
       <c r="F52">
-        <v>8.016459952319886</v>
+        <v>5.467076433464128</v>
       </c>
       <c r="G52">
-        <v>-8.65122500116858</v>
+        <v>-9.808794030238845</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-3.088639285008549</v>
       </c>
       <c r="E53">
-        <v>-18.71193291331599</v>
+        <v>-17.27631608340433</v>
       </c>
       <c r="F53">
-        <v>7.958939776604295</v>
+        <v>6.290346063266806</v>
       </c>
       <c r="G53">
-        <v>-8.502697226058757</v>
+        <v>-10.3874308898038</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-2.904766329020271</v>
       </c>
       <c r="E54">
-        <v>-16.03968945833772</v>
+        <v>-17.85582490216591</v>
       </c>
       <c r="F54">
-        <v>7.927925701043481</v>
+        <v>5.089317703500275</v>
       </c>
       <c r="G54">
-        <v>-8.144240176797219</v>
+        <v>-9.822673597435296</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-2.72980130223985</v>
       </c>
       <c r="E55">
-        <v>-14.52902222869695</v>
+        <v>-15.75565904010263</v>
       </c>
       <c r="F55">
-        <v>8.428672139300977</v>
+        <v>5.997496648824708</v>
       </c>
       <c r="G55">
-        <v>-7.234298376375128</v>
+        <v>-9.065449692054441</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-2.56759884178175</v>
       </c>
       <c r="E56">
-        <v>-13.88836995388381</v>
+        <v>-16.52007903801941</v>
       </c>
       <c r="F56">
-        <v>7.961661791889894</v>
+        <v>6.394428770693758</v>
       </c>
       <c r="G56">
-        <v>-8.944284023528827</v>
+        <v>-10.46116321946608</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-2.420092216264011</v>
       </c>
       <c r="E57">
-        <v>-16.17689316382212</v>
+        <v>-15.83625229201714</v>
       </c>
       <c r="F57">
-        <v>8.524370111876792</v>
+        <v>5.933964182499596</v>
       </c>
       <c r="G57">
-        <v>-8.430989410098652</v>
+        <v>-10.07860887907198</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-2.288591488635932</v>
       </c>
       <c r="E58">
-        <v>-14.60540399978432</v>
+        <v>-15.19765594440348</v>
       </c>
       <c r="F58">
-        <v>8.383082110920503</v>
+        <v>5.806602694319173</v>
       </c>
       <c r="G58">
-        <v>-8.438122785768885</v>
+        <v>-10.9096799568697</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-2.173691970199687</v>
       </c>
       <c r="E59">
-        <v>-13.6824964685471</v>
+        <v>-14.30172906130396</v>
       </c>
       <c r="F59">
-        <v>8.096927561827831</v>
+        <v>5.658257003091031</v>
       </c>
       <c r="G59">
-        <v>-9.193617487387911</v>
+        <v>-9.514786734847918</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-2.075203435338067</v>
       </c>
       <c r="E60">
-        <v>-13.08902183594586</v>
+        <v>-15.33737295296214</v>
       </c>
       <c r="F60">
-        <v>8.236025359371117</v>
+        <v>6.498650643844381</v>
       </c>
       <c r="G60">
-        <v>-7.863849950877989</v>
+        <v>-11.3854964576479</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-1.992522151779231</v>
       </c>
       <c r="E61">
-        <v>-12.73258564680213</v>
+        <v>-13.79688119350684</v>
       </c>
       <c r="F61">
-        <v>8.242014455693358</v>
+        <v>5.451009419319429</v>
       </c>
       <c r="G61">
-        <v>-8.277024650864828</v>
+        <v>-11.08853606285347</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-1.924439057708271</v>
       </c>
       <c r="E62">
-        <v>-12.92843761915987</v>
+        <v>-13.7887706965591</v>
       </c>
       <c r="F62">
-        <v>8.146526888437855</v>
+        <v>5.92314404748423</v>
       </c>
       <c r="G62">
-        <v>-7.847187907799129</v>
+        <v>-9.746490195268107</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-1.868175186491333</v>
       </c>
       <c r="E63">
-        <v>-11.77287067883056</v>
+        <v>-14.35953503201187</v>
       </c>
       <c r="F63">
-        <v>7.913069760041675</v>
+        <v>6.110731159317789</v>
       </c>
       <c r="G63">
-        <v>-7.881903231898054</v>
+        <v>-10.51667820703033</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-1.821202556937301</v>
       </c>
       <c r="E64">
-        <v>-13.37427494216303</v>
+        <v>-12.49635780019201</v>
       </c>
       <c r="F64">
-        <v>7.761958978422989</v>
+        <v>5.553753485023457</v>
       </c>
       <c r="G64">
-        <v>-8.497266804377876</v>
+        <v>-11.1505084944467</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-1.780934512146342</v>
       </c>
       <c r="E65">
-        <v>-11.17835902568157</v>
+        <v>-11.88643574999492</v>
       </c>
       <c r="F65">
-        <v>7.823398988688628</v>
+        <v>5.690336359131845</v>
       </c>
       <c r="G65">
-        <v>-7.63173305654131</v>
+        <v>-11.00240071569649</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-1.74401035952817</v>
       </c>
       <c r="E66">
-        <v>-13.65336479525575</v>
+        <v>-13.53589617949678</v>
       </c>
       <c r="F66">
-        <v>7.776120747541249</v>
+        <v>5.558049398374376</v>
       </c>
       <c r="G66">
-        <v>-7.624917959362343</v>
+        <v>-9.634052576090616</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-1.707445026538842</v>
       </c>
       <c r="E67">
-        <v>-12.23989673171561</v>
+        <v>-11.58741608279444</v>
       </c>
       <c r="F67">
-        <v>7.576795669610021</v>
+        <v>5.116986831488584</v>
       </c>
       <c r="G67">
-        <v>-7.962654094475988</v>
+        <v>-11.2402597477622</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-1.668728698705196</v>
       </c>
       <c r="E68">
-        <v>-12.6863997403979</v>
+        <v>-12.46294671896342</v>
       </c>
       <c r="F68">
-        <v>7.480705050885279</v>
+        <v>6.063719652474111</v>
       </c>
       <c r="G68">
-        <v>-6.987271611272333</v>
+        <v>-10.34675686735292</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-1.625783465025908</v>
       </c>
       <c r="E69">
-        <v>-12.98387972643578</v>
+        <v>-13.85204706386828</v>
       </c>
       <c r="F69">
-        <v>7.505247920295422</v>
+        <v>4.846160392817314</v>
       </c>
       <c r="G69">
-        <v>-6.321019573627083</v>
+        <v>-9.732111882394621</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-1.57833123399023</v>
       </c>
       <c r="E70">
-        <v>-11.67779989551353</v>
+        <v>-12.27852914347505</v>
       </c>
       <c r="F70">
-        <v>7.30889833807505</v>
+        <v>5.500068650382827</v>
       </c>
       <c r="G70">
-        <v>-5.954654780407284</v>
+        <v>-8.499665377337829</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-1.526786031288217</v>
       </c>
       <c r="E71">
-        <v>-11.11052248504667</v>
+        <v>-11.95261939761702</v>
       </c>
       <c r="F71">
-        <v>7.099460550890445</v>
+        <v>5.068149602889137</v>
       </c>
       <c r="G71">
-        <v>-5.841177013995448</v>
+        <v>-9.927659562451289</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-1.472686658652657</v>
       </c>
       <c r="E72">
-        <v>-13.1738809103756</v>
+        <v>-13.2979792120818</v>
       </c>
       <c r="F72">
-        <v>7.048809197678866</v>
+        <v>5.697823143718347</v>
       </c>
       <c r="G72">
-        <v>-5.685732423838314</v>
+        <v>-7.699929965432809</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-1.419542683576022</v>
       </c>
       <c r="E73">
-        <v>-12.01667919092952</v>
+        <v>-14.91375685191461</v>
       </c>
       <c r="F73">
-        <v>6.170524375186663</v>
+        <v>4.605296003105302</v>
       </c>
       <c r="G73">
-        <v>-5.914653408376093</v>
+        <v>-8.137749920552636</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-1.370798745944083</v>
       </c>
       <c r="E74">
-        <v>-11.63923541086421</v>
+        <v>-13.15648251323813</v>
       </c>
       <c r="F74">
-        <v>6.468378785476475</v>
+        <v>4.802483893137307</v>
       </c>
       <c r="G74">
-        <v>-4.065301156706541</v>
+        <v>-8.782598549965629</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-1.329929299138463</v>
       </c>
       <c r="E75">
-        <v>-12.51009719033128</v>
+        <v>-10.74233037737902</v>
       </c>
       <c r="F75">
-        <v>6.486611152012093</v>
+        <v>6.182295475980443</v>
       </c>
       <c r="G75">
-        <v>-5.491910666321915</v>
+        <v>-6.776184065910136</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-1.30038850040767</v>
       </c>
       <c r="E76">
-        <v>-11.36293962623422</v>
+        <v>-13.55233001167062</v>
       </c>
       <c r="F76">
-        <v>6.767739167704578</v>
+        <v>4.445015194337626</v>
       </c>
       <c r="G76">
-        <v>-5.010473433012389</v>
+        <v>-7.16562569035751</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-1.284383546455795</v>
       </c>
       <c r="E77">
-        <v>-11.15740577644808</v>
+        <v>-12.71399173252664</v>
       </c>
       <c r="F77">
-        <v>6.362157233415495</v>
+        <v>4.979441394458143</v>
       </c>
       <c r="G77">
-        <v>-4.56976928414181</v>
+        <v>-4.986021769951407</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-1.284232253888843</v>
       </c>
       <c r="E78">
-        <v>-12.71035083942447</v>
+        <v>-13.27641461885727</v>
       </c>
       <c r="F78">
-        <v>6.167378235790831</v>
+        <v>4.850307200035728</v>
       </c>
       <c r="G78">
-        <v>-5.039377713729537</v>
+        <v>-4.146767325584435</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-1.301126990243087</v>
       </c>
       <c r="E79">
-        <v>-13.67160548855865</v>
+        <v>-13.12362390583847</v>
       </c>
       <c r="F79">
-        <v>5.54074977353431</v>
+        <v>3.980721892007725</v>
       </c>
       <c r="G79">
-        <v>-3.316608427380243</v>
+        <v>-7.151568937196849</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-1.335093585274422</v>
       </c>
       <c r="E80">
-        <v>-14.44127851632433</v>
+        <v>-14.44503262127668</v>
       </c>
       <c r="F80">
-        <v>5.490131555018844</v>
+        <v>3.732432016897018</v>
       </c>
       <c r="G80">
-        <v>-1.713895756669472</v>
+        <v>-4.580643252389809</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-1.386080795373019</v>
       </c>
       <c r="E81">
-        <v>-14.84765471682465</v>
+        <v>-13.62731248428963</v>
       </c>
       <c r="F81">
-        <v>6.019423533976811</v>
+        <v>3.958929202374875</v>
       </c>
       <c r="G81">
-        <v>-3.484022913786231</v>
+        <v>-6.262197114730919</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-1.453257936071605</v>
       </c>
       <c r="E82">
-        <v>-15.07416898668832</v>
+        <v>-14.79947628185704</v>
       </c>
       <c r="F82">
-        <v>5.612333971014633</v>
+        <v>4.146030890910394</v>
       </c>
       <c r="G82">
-        <v>-2.171868974607408</v>
+        <v>-4.500906287273743</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-1.535654936884559</v>
       </c>
       <c r="E83">
-        <v>-15.35519249818232</v>
+        <v>-14.58611722898566</v>
       </c>
       <c r="F83">
-        <v>5.903599546982578</v>
+        <v>3.61904177333221</v>
       </c>
       <c r="G83">
-        <v>-1.308730518509238</v>
+        <v>-3.764777355298559</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-1.632458555725301</v>
       </c>
       <c r="E84">
-        <v>-16.55450902589973</v>
+        <v>-16.45632718093943</v>
       </c>
       <c r="F84">
-        <v>5.207805720061911</v>
+        <v>3.573476595973821</v>
       </c>
       <c r="G84">
-        <v>-2.278098522594431</v>
+        <v>-5.950664814990999</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-1.743120504990713</v>
       </c>
       <c r="E85">
-        <v>-16.30064730150374</v>
+        <v>-19.25215269158701</v>
       </c>
       <c r="F85">
-        <v>5.409266329157556</v>
+        <v>3.514571389960748</v>
       </c>
       <c r="G85">
-        <v>-2.243540697130359</v>
+        <v>-2.674496336747828</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-1.867712969044528</v>
       </c>
       <c r="E86">
-        <v>-18.8149647539385</v>
+        <v>-17.17389558677285</v>
       </c>
       <c r="F86">
-        <v>5.141710284992539</v>
+        <v>2.932653229902929</v>
       </c>
       <c r="G86">
-        <v>-1.68506694404819</v>
+        <v>-4.110942948598417</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-2.008813698550732</v>
       </c>
       <c r="E87">
-        <v>-18.14732730251366</v>
+        <v>-20.8902330659076</v>
       </c>
       <c r="F87">
-        <v>5.494881413706496</v>
+        <v>2.655315823445654</v>
       </c>
       <c r="G87">
-        <v>-1.828689292926645</v>
+        <v>-2.874020857334543</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-2.168930156665511</v>
       </c>
       <c r="E88">
-        <v>-19.70023160922397</v>
+        <v>-21.88505276438664</v>
       </c>
       <c r="F88">
-        <v>4.570632140767754</v>
+        <v>3.252323524112869</v>
       </c>
       <c r="G88">
-        <v>-1.235864431338649</v>
+        <v>-2.910117575709994</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-2.350489920439613</v>
       </c>
       <c r="E89">
-        <v>-20.26135935198841</v>
+        <v>-21.35383559244286</v>
       </c>
       <c r="F89">
-        <v>4.908276350883638</v>
+        <v>2.479597559759406</v>
       </c>
       <c r="G89">
-        <v>-1.167802052531087</v>
+        <v>-2.69186056124041</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-2.556366483643783</v>
       </c>
       <c r="E90">
-        <v>-24.14665872482336</v>
+        <v>-26.2274427181338</v>
       </c>
       <c r="F90">
-        <v>4.08012432360886</v>
+        <v>1.708440523266846</v>
       </c>
       <c r="G90">
-        <v>-1.25009837046352</v>
+        <v>-1.367064075393046</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-2.788393653771982</v>
       </c>
       <c r="E91">
-        <v>-24.64962727590729</v>
+        <v>-24.76168436522709</v>
       </c>
       <c r="F91">
-        <v>3.873468194162856</v>
+        <v>2.253802829839123</v>
       </c>
       <c r="G91">
-        <v>-1.543990823099865</v>
+        <v>0.1434758004913636</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-3.047707410516133</v>
       </c>
       <c r="E92">
-        <v>-27.65596342927544</v>
+        <v>-27.23990987982073</v>
       </c>
       <c r="F92">
-        <v>3.551675622666943</v>
+        <v>1.522324591940659</v>
       </c>
       <c r="G92">
-        <v>-0.8178302422222736</v>
+        <v>-2.454293557893493</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-3.334033941135491</v>
       </c>
       <c r="E93">
-        <v>-25.63324352969135</v>
+        <v>-27.13100007993626</v>
       </c>
       <c r="F93">
-        <v>3.319321879651293</v>
+        <v>0.6349550641419525</v>
       </c>
       <c r="G93">
-        <v>-0.2105844118805184</v>
+        <v>-1.354667620341464</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-3.643357219969436</v>
       </c>
       <c r="E94">
-        <v>-29.91662746711857</v>
+        <v>-30.69520800325733</v>
       </c>
       <c r="F94">
-        <v>3.340186797793007</v>
+        <v>1.573762894184897</v>
       </c>
       <c r="G94">
-        <v>-1.120618086506272</v>
+        <v>-2.369910383049254</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-3.974450533181815</v>
       </c>
       <c r="E95">
-        <v>-30.49053682776966</v>
+        <v>-32.05480081152822</v>
       </c>
       <c r="F95">
-        <v>2.723974227259288</v>
+        <v>0.2957850012701117</v>
       </c>
       <c r="G95">
-        <v>-0.9820094441706494</v>
+        <v>-0.8267518836424038</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-4.323895003383271</v>
       </c>
       <c r="E96">
-        <v>-32.94631243247026</v>
+        <v>-34.07234466532154</v>
       </c>
       <c r="F96">
-        <v>2.470482204859</v>
+        <v>0.5766545663329233</v>
       </c>
       <c r="G96">
-        <v>-0.1006667708606799</v>
+        <v>-3.790219947270493</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-4.683716852484898</v>
       </c>
       <c r="E97">
-        <v>-35.95450752441857</v>
+        <v>-33.826419091624</v>
       </c>
       <c r="F97">
-        <v>1.414141465869849</v>
+        <v>-0.3788962256554044</v>
       </c>
       <c r="G97">
-        <v>-0.3142775756020903</v>
+        <v>-2.219285907362944</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-5.050638764298312</v>
       </c>
       <c r="E98">
-        <v>-36.79127215884488</v>
+        <v>-37.65191090823964</v>
       </c>
       <c r="F98">
-        <v>1.017590393006086</v>
+        <v>-1.25397692303358</v>
       </c>
       <c r="G98">
-        <v>-2.111602778225087</v>
+        <v>-5.155870922754503</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-5.41083168251682</v>
       </c>
       <c r="E99">
-        <v>-40.01465354292667</v>
+        <v>-40.0537569159829</v>
       </c>
       <c r="F99">
-        <v>0.1892610951071093</v>
+        <v>-0.5772338896424957</v>
       </c>
       <c r="G99">
-        <v>-0.9151479924538445</v>
+        <v>-0.5519200470448739</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-5.764107157784964</v>
       </c>
       <c r="E100">
-        <v>-42.5436523080943</v>
+        <v>-42.80623134495506</v>
       </c>
       <c r="F100">
-        <v>0.5069698153072205</v>
+        <v>-1.403675338230493</v>
       </c>
       <c r="G100">
-        <v>-1.991132728670075</v>
+        <v>-3.94103801502881</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-6.087329517311497</v>
       </c>
       <c r="E101">
-        <v>-44.4931648968704</v>
+        <v>-45.60123493757025</v>
       </c>
       <c r="F101">
-        <v>0.4217258393547346</v>
+        <v>-1.233873274535038</v>
       </c>
       <c r="G101">
-        <v>-1.540286323959252</v>
+        <v>-5.848064298048723</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-6.392922791826407</v>
       </c>
       <c r="E102">
-        <v>-46.14635452471758</v>
+        <v>-45.96968290401934</v>
       </c>
       <c r="F102">
-        <v>-0.2331565782764706</v>
+        <v>-2.322575842849359</v>
       </c>
       <c r="G102">
-        <v>-2.694390383062741</v>
+        <v>-3.606619194911764</v>
       </c>
     </row>
   </sheetData>
